--- a/www/download/IND.compensation.empe.s.us.EXI382.xlsx
+++ b/www/download/IND.compensation.empe.s.us.EXI382.xlsx
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -673,7 +678,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Austrália</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -683,144 +688,144 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.153</t>
+          <t>169277.54628597</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.187</t>
+          <t>207436.239554044</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.215</t>
+          <t>238716.834138694</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>0.186</t>
+          <t>206515.586265252</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>0.223</t>
+          <t>247058.797324555</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.239</t>
+          <t>265133.124936434</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.239</t>
+          <t>265045.627882214</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>0.245</t>
+          <t>272197.275394199</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>0.259</t>
+          <t>287831.954690131</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0.282</t>
+          <t>312841.713422113</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>0.316</t>
+          <t>350819.780311208</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>0.338</t>
+          <t>374465.180421657</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>0.366</t>
+          <t>405719.153097115</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>0.363</t>
+          <t>402603.061872046</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>0.368</t>
+          <t>407889.477523641</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>0.482</t>
+          <t>534527.555333532</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>0.546</t>
+          <t>606263.381433462</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.591</t>
+          <t>655924.890922854</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>0.565</t>
+          <t>627292.139092732</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>0.548</t>
+          <t>608117.499625769</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.557</t>
+          <t>617566.146918964</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>0.579</t>
+          <t>642301.961064515</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>0.611</t>
+          <t>678245.691859897</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>0.597</t>
+          <t>662372.520938505</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0.595</t>
+          <t>659680.563920622</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>676825.633587905</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>0.622</t>
+          <t>689612.772506665</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Áustria</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -830,144 +835,144 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.097</t>
+          <t>126317.228016736</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>0.095</t>
+          <t>124751.628965015</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0.104</t>
+          <t>135498.165200572</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>0.109</t>
+          <t>142219.15348384</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>0.114</t>
+          <t>149158.440885337</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0.111</t>
+          <t>145445.606079907</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.117</t>
+          <t>153240.637505541</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>0.123</t>
+          <t>160737.984917007</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>0.124</t>
+          <t>161822.076886734</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0.126</t>
+          <t>164818.750446744</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>0.136</t>
+          <t>177798.678438721</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>0.143</t>
+          <t>186683.374528114</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>0.145</t>
+          <t>189260.600007733</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>0.147</t>
+          <t>192644.57267525</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>0.156</t>
+          <t>204011.98934295</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>0.161</t>
+          <t>210316.615546683</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>0.167</t>
+          <t>218576.826698087</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>0.162</t>
+          <t>211825.778896267</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>0.169</t>
+          <t>221555.552742093</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>0.172</t>
+          <t>224813.801965894</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>0.177</t>
+          <t>231135.833575785</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>0.195</t>
+          <t>254596.000438183</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>0.199</t>
+          <t>259993.147232401</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>0.218</t>
+          <t>284978.487946371</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>0.217</t>
+          <t>284078.972998634</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>0.221</t>
+          <t>289053.113290093</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>0.217</t>
+          <t>284289.42787834</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Bélgica</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -977,144 +982,144 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.123</t>
+          <t>158440.73917837</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>154606.52166269</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.125</t>
+          <t>161417.011957709</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0.124</t>
+          <t>160464.636346243</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.137</t>
+          <t>176569.290287449</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.136</t>
+          <t>175616.881120787</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.145</t>
+          <t>187707.458280077</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.152</t>
+          <t>197018.059867612</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.157</t>
+          <t>202604.300818084</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0.162</t>
+          <t>209933.566433836</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0.178</t>
+          <t>230470.507516846</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.183</t>
+          <t>235745.35114065</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.192</t>
+          <t>248586.46048159</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0.189</t>
+          <t>244548.441230792</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0.203</t>
+          <t>261890.402596481</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>258682.76187317</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>0.205</t>
+          <t>265068.779857778</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>0.211</t>
+          <t>272737.42011345</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>0.214</t>
+          <t>276576.575334175</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>0.215</t>
+          <t>277604.033637769</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>0.224</t>
+          <t>288548.918981303</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>0.232</t>
+          <t>299466.000884003</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>309781.859074384</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>0.248</t>
+          <t>320537.27519245</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0.253</t>
+          <t>327103.428532982</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>0.258</t>
+          <t>332936.099565425</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>0.261</t>
+          <t>336757.238124152</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1124,144 +1129,144 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>6849.35756134678</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3912.50230921894</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>4680.81455265754</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>6745.56938840025</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>6605.33303147635</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>7437.2696985272</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>7672.11085667238</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>7883.67058111154</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>8917.42504960623</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>9569.59773883571</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>11869.1940357693</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>14633.5672815863</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>16674.6767967814</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>19627.1183082369</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>20359.8862011246</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>21273.3593112703</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>23292.9559817037</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>23612.7538313717</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>23275.7153413398</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>24554.8061918618</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>26108.3621508289</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>27915.4844392295</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>27263.8150900026</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>33310.919240621</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>35361.8982483466</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>38056.9464699534</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>38208.4951236881</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1271,144 +1276,144 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.277</t>
+          <t>368096.300987938</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>0.322</t>
+          <t>427391.041370651</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0.357</t>
+          <t>473674.038022653</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>0.356</t>
+          <t>472411.739936025</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>0.262</t>
+          <t>347852.356428172</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>0.314</t>
+          <t>416738.292762905</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0.283</t>
+          <t>375595.677628965</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>0.239</t>
+          <t>317300.308441144</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>0.212</t>
+          <t>281571.85707335</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0.228</t>
+          <t>302853.28139726</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>0.306</t>
+          <t>406452.845203183</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>0.377</t>
+          <t>501052.627508162</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>0.449</t>
+          <t>596347.326719196</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>0.515</t>
+          <t>684155.294353757</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>0.559</t>
+          <t>741809.701320059</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>0.775</t>
+          <t>1029851.42274988</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>0.878</t>
+          <t>1166209.65203946</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>0.896</t>
+          <t>1189332.52998873</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>0.869</t>
+          <t>1154604.39063755</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>0.866</t>
+          <t>1150641.91302489</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>0.767</t>
+          <t>1018669.92381262</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>1023119.80230013</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>0.853</t>
+          <t>1132797.41304694</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>0.766</t>
+          <t>1017753.79047634</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>0.777</t>
+          <t>1032373.48460109</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>1048606.23989371</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>0.828</t>
+          <t>1100168.52504271</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Canadá</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1418,144 +1423,144 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.278</t>
+          <t>356612.496345456</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>0.285</t>
+          <t>365579.587323201</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0.303</t>
+          <t>389271.929843819</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>0.302</t>
+          <t>387549.155432561</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>462124.656787504</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>0.446</t>
+          <t>572435.08872821</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>0.464</t>
+          <t>596140.759163547</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>0.453</t>
+          <t>581849.425756318</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>0.446</t>
+          <t>572829.926567168</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>0.442</t>
+          <t>567928.467966216</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>616395.785165716</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>693354.838594691</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>720034.356954033</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>693985.688594176</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>0.523</t>
+          <t>672558.542730378</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>0.648</t>
+          <t>832724.640226658</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>0.706</t>
+          <t>906628.219428936</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>0.752</t>
+          <t>966796.843627544</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>0.746</t>
+          <t>959070.721360659</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>0.712</t>
+          <t>914547.585718988</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>0.762</t>
+          <t>978666.993958838</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>0.742</t>
+          <t>953210.461761621</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>0.791</t>
+          <t>1015705.44055156</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>0.792</t>
+          <t>1017305.29355856</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>1118405.63541209</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>0.882</t>
+          <t>1133019.34872544</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>0.811</t>
+          <t>1042524.94669946</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1565,144 +1570,144 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>0.276</t>
+          <t>383713.166167558</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>0.356</t>
+          <t>493808.957453354</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0.484</t>
+          <t>672931.679676664</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>0.617</t>
+          <t>857301.78752166</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>833577.724720378</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>0.756</t>
+          <t>1050362.64164637</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>0.817</t>
+          <t>1135291.35951842</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>0.892</t>
+          <t>1238509.09088636</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>0.791</t>
+          <t>1099208.13895123</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>0.712</t>
+          <t>988924.69602168</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>0.871</t>
+          <t>1210221.22515616</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>1.049</t>
+          <t>1457281.94853316</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>1.118</t>
+          <t>1552547.81780608</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>1.335</t>
+          <t>1850516.84746682</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>1.722</t>
+          <t>2386515.92707981</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>2.232</t>
+          <t>3095247.32572743</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>2.748</t>
+          <t>3812696.7655739</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>3.175</t>
+          <t>4408189.81255738</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>3.678</t>
+          <t>5101748.10240916</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>3.876</t>
+          <t>5375738.82682761</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>4.874</t>
+          <t>6758653.09040043</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>4.916</t>
+          <t>6814641.04487174</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>5.377</t>
+          <t>7459191.69926893</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>5.645</t>
+          <t>7823176.96811613</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>6.11</t>
+          <t>8467964.97717361</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>6.503</t>
+          <t>9012007.10697801</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>6.879</t>
+          <t>9532839.94794653</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Chipre</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1712,144 +1717,144 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3775.97036719255</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>4396.1098510705</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>4773.45055706021</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>5518.59681756397</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>5714.36621945998</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>6664.04031303083</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>6323.67865270112</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>6921.64758087576</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>7831.89439344073</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>7974.29927829446</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>8828.01157329718</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>9837.50467673848</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>10448.3469233734</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>10334.6285670715</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>10877.3709448485</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>10446.4251000842</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>10271.5244316107</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>10055.0231504971</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>9900.81623755864</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>8552.48090032617</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>9329.45351161145</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>10116.7592007911</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>9658.08346272405</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>10994.9234640065</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>11874.9497812925</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>11190.7304835376</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>12532.3412619706</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>República Tcheca</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1859,144 +1864,144 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>23892.6509255471</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>26495.1831155095</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>30518.2093728689</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>30371.6097231001</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>30403.610157945</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>32187.8676495556</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>0.034</t>
+          <t>38337.2962842937</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>0.039</t>
+          <t>44509.5615156856</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>45270.0771346559</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>0.043</t>
+          <t>49149.5036967326</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>0.051</t>
+          <t>58278.2319754728</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>0.058</t>
+          <t>66028.1595614725</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>0.065</t>
+          <t>73510.1433384987</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>0.076</t>
+          <t>85857.7211216228</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>0.068</t>
+          <t>76861.4030245589</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>0.073</t>
+          <t>82879.9423775327</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>0.073</t>
+          <t>82916.9184622124</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>0.075</t>
+          <t>85611.1147698549</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>0.074</t>
+          <t>83788.3688546218</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>0.071</t>
+          <t>80889.9944458741</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>0.078</t>
+          <t>87965.7414493917</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>0.081</t>
+          <t>92158.3921061505</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>0.088</t>
+          <t>99353.9665425821</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>0.098</t>
+          <t>110712.053934333</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>0.105</t>
+          <t>119214.185938358</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>0.105</t>
+          <t>119260.072569702</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>125297.774756873</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Alemanha</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2006,144 +2011,144 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>1.137</t>
+          <t>1276881.61016686</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1.123</t>
+          <t>1260925.13296489</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1.117</t>
+          <t>1253887.92200283</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>1.137</t>
+          <t>1276707.78587048</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>1.171</t>
+          <t>1314885.93780704</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>1.217</t>
+          <t>1366459.67760715</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1.185</t>
+          <t>1330617.66616972</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>1.229</t>
+          <t>1379517.92305336</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>1.378</t>
+          <t>1546598.54184584</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1425531.9658001</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1403145.40281526</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>1.282</t>
+          <t>1438491.01000578</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>1.317</t>
+          <t>1477941.99173003</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>1.371</t>
+          <t>1538641.27649132</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>1.363</t>
+          <t>1530039.80652916</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>1.405</t>
+          <t>1577381.45250843</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>1.463</t>
+          <t>1642062.99909761</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1672633.44107859</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>1.528</t>
+          <t>1714651.38131562</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>1.591</t>
+          <t>1785336.44090186</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>1.605</t>
+          <t>1801548.90083513</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1851836.94279276</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1964196.34351389</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>1.832</t>
+          <t>2055701.41997646</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>2064724.67263133</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>1.883</t>
+          <t>2112840.45636819</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>1.886</t>
+          <t>2115963.78567541</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Dinamarca</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2153,144 +2158,144 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>89816.4622472036</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>0.083</t>
+          <t>92825.5722034932</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0.085</t>
+          <t>94911.5320695377</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>0.085</t>
+          <t>95540.0618419792</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>0.097</t>
+          <t>108397.352776446</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>0.105</t>
+          <t>117754.334584164</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>0.108</t>
+          <t>121396.863132412</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>0.113</t>
+          <t>127198.223822843</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>0.116</t>
+          <t>129934.947954409</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>0.119</t>
+          <t>133533.801667309</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>0.123</t>
+          <t>137563.502039762</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>0.133</t>
+          <t>149206.569886388</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>0.142</t>
+          <t>159718.018372517</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>0.146</t>
+          <t>163746.021693138</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>0.143</t>
+          <t>160373.795248516</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>0.145</t>
+          <t>162713.488159464</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>0.147</t>
+          <t>164808.764808818</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>168487.746165714</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>0.163</t>
+          <t>182515.604755083</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>0.169</t>
+          <t>189737.04462506</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>0.175</t>
+          <t>196071.13713157</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>0.182</t>
+          <t>204400.617544806</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>213104.181860846</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>0.173</t>
+          <t>194165.338842966</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>0.166</t>
+          <t>186559.23122037</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>0.193</t>
+          <t>216565.125251845</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>0.205</t>
+          <t>230204.257044796</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Espanha</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2300,144 +2305,144 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>0.226</t>
+          <t>240663.258797474</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>0.246</t>
+          <t>261756.458419507</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0.251</t>
+          <t>267955.189121265</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>0.278</t>
+          <t>296178.976068549</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>0.301</t>
+          <t>320649.318823336</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>0.334</t>
+          <t>355823.401375211</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>0.362</t>
+          <t>386153.007151631</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>0.388</t>
+          <t>413342.439562233</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>0.401</t>
+          <t>427259.067940935</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>0.426</t>
+          <t>454145.270202545</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>490490.30775944</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>0.495</t>
+          <t>527183.167745986</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>553828.28452303</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>0.577</t>
+          <t>614802.597933762</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>0.541</t>
+          <t>576998.493924958</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>0.541</t>
+          <t>577083.916268271</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>0.536</t>
+          <t>571058.698602303</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>0.518</t>
+          <t>552269.571799132</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>0.516</t>
+          <t>550087.084238168</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>0.517</t>
+          <t>551305.225284563</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>0.545</t>
+          <t>581265.106824652</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>0.562</t>
+          <t>598667.502317449</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>0.595</t>
+          <t>633956.361979667</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>0.628</t>
+          <t>669847.628394944</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>0.624</t>
+          <t>665104.34798183</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>0.639</t>
+          <t>680895.568105966</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>0.716</t>
+          <t>763560.966914084</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Estônia</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2447,144 +2452,144 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>2167.9752341741</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>2343.72159400129</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3060.77854650594</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3041.03505838252</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>2976.87933263442</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3588.11012417577</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3583.78419802002</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>4351.83788420848</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>4983.73857715163</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>4842.55383232829</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>6215.58801241625</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>7609.14608361905</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>9495.13702806671</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>10002.6500586918</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>9196.92272624815</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>8619.72920313491</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>10157.124899463</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>10464.1498668138</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>11415.2710565818</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>11620.2312973966</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>12259.5220705441</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>13736.8168844295</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>13941.8686318838</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>15635.5085505895</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>16722.1281414158</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>17061.356644428</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>17825.6438403032</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Finlândia</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2594,144 +2599,144 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.051</t>
+          <t>46843.5806233725</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>0.056</t>
+          <t>51782.7600832847</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0.059</t>
+          <t>54618.6660290064</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>0.062</t>
+          <t>57410.639932247</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>0.064</t>
+          <t>58888.7507419737</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>64228.2965664495</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>0.076</t>
+          <t>69771.4853563246</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>0.078</t>
+          <t>71908.2702203902</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>0.081</t>
+          <t>74698.8432885357</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0.083</t>
+          <t>76364.5337024765</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>0.087</t>
+          <t>80826.0680139168</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>83560.8398509499</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>0.096</t>
+          <t>88794.928831558</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>0.104</t>
+          <t>95940.6565768251</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>0.103</t>
+          <t>95186.5532996791</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>0.104</t>
+          <t>96160.8833735</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>0.109</t>
+          <t>100717.095992916</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>0.111</t>
+          <t>102884.375841087</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>0.113</t>
+          <t>104154.747429103</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>0.116</t>
+          <t>107288.675934895</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>0.119</t>
+          <t>109887.822879017</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>0.121</t>
+          <t>112109.486930217</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>0.129</t>
+          <t>118741.785184818</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>0.147</t>
+          <t>136282.28424214</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>0.134</t>
+          <t>123755.086232096</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>0.144</t>
+          <t>132763.658777584</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>0.156</t>
+          <t>143869.197296508</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>França</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2741,144 +2746,144 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.685</t>
+          <t>631703.529051598</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0.697</t>
+          <t>642779.131712734</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0.708</t>
+          <t>652938.833860273</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>0.663</t>
+          <t>611637.512414026</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>738186.642430512</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.804</t>
+          <t>741518.842811516</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.839</t>
+          <t>773858.860104278</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.873</t>
+          <t>805624.777568501</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.909</t>
+          <t>838599.318091709</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0.939</t>
+          <t>866562.770545418</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>0.974</t>
+          <t>898566.429190504</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0.988</t>
+          <t>910765.156446547</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>1.086</t>
+          <t>1001516.22000447</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>1.111</t>
+          <t>1024808.33885928</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>1.065</t>
+          <t>981987.671695375</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>1.135</t>
+          <t>1046626.54861545</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>1.158</t>
+          <t>1067952.66301798</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>1.202</t>
+          <t>1108451.4457385</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>1.213</t>
+          <t>1118665.26012465</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1143578.53095271</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>1.271</t>
+          <t>1172368.68881578</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>1.351</t>
+          <t>1246250.24598914</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>1.309</t>
+          <t>1207499.2633138</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>1.369</t>
+          <t>1262284.39080028</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>1.406</t>
+          <t>1297006.47639092</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>1.494</t>
+          <t>1377346.10386089</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>1.508</t>
+          <t>1390440.89076182</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Reino Unido</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2888,144 +2893,144 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.585</t>
+          <t>775792.940825431</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>0.628</t>
+          <t>833705.815963904</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0.775</t>
+          <t>1027506.22851103</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>0.844</t>
+          <t>1119909.10133354</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>0.924</t>
+          <t>1226237.2592844</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>1.066</t>
+          <t>1413617.31918309</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1433118.18118687</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>1.119</t>
+          <t>1483845.79074451</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>1.075</t>
+          <t>1425844.04212145</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>1.147</t>
+          <t>1520956.86474657</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>1.205</t>
+          <t>1598837.06685805</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>1.265</t>
+          <t>1678416.45976675</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>1.321</t>
+          <t>1752719.9410312</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>1.162</t>
+          <t>1541576.81568826</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>1.052</t>
+          <t>1395148.53574731</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>1.126</t>
+          <t>1494009.20163338</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>1.141</t>
+          <t>1514196.76652146</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>1.244</t>
+          <t>1650501.03010506</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>1.243</t>
+          <t>1648960.06174615</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1816951.91548278</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>1.586</t>
+          <t>2104058.33366382</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>1.433</t>
+          <t>1901432.99988731</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>1.406</t>
+          <t>1864809.94132948</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>1.455</t>
+          <t>1930121.9692226</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>1.521</t>
+          <t>2017101.67207394</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>1.544</t>
+          <t>2048283.47099292</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>1.565</t>
+          <t>2075347.60032388</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Grécia</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -3035,144 +3040,144 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0.037</t>
+          <t>32789.5464067325</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>0.044</t>
+          <t>39609.1800922822</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>0.048</t>
+          <t>42547.0769904714</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>0.048</t>
+          <t>43332.3557603831</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>0.051</t>
+          <t>45293.4675051833</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>0.056</t>
+          <t>50137.5482177656</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0.056</t>
+          <t>49923.3267877192</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>0.064</t>
+          <t>57393.3056608165</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>0.069</t>
+          <t>61812.5336645465</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0.075</t>
+          <t>67593.131484678</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>0.078</t>
+          <t>69526.5562370285</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>0.084</t>
+          <t>75632.4063306604</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>0.092</t>
+          <t>82093.5821113811</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>0.097</t>
+          <t>86817.507643315</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>0.096</t>
+          <t>85985.95954308</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>0.096</t>
+          <t>85622.1404446432</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>0.082</t>
+          <t>73033.4943346942</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>0.075</t>
+          <t>67483.8826949643</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>0.075</t>
+          <t>66940.4766673623</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>0.073</t>
+          <t>65053.2534881922</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>62925.4855510833</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>0.068</t>
+          <t>60777.8633000031</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>0.072</t>
+          <t>64050.8166741695</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>0.071</t>
+          <t>63798.2548048081</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>0.072</t>
+          <t>64742.317790655</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>0.065</t>
+          <t>58469.8180056114</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>0.075</t>
+          <t>67479.5683093736</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Hungria</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3182,144 +3187,144 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>16182.9572842615</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>17219.4023329625</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>18474.8539456442</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>19675.9002115117</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>20120.3035705146</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>22529.0115783358</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>28542.4767724727</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.032</t>
+          <t>30553.8588942691</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>0.038</t>
+          <t>35564.7396853465</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0.042</t>
+          <t>39386.146508755</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>0.045</t>
+          <t>42134.7589433616</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>0.046</t>
+          <t>43873.9016577257</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>0.051</t>
+          <t>48581.9463915817</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>0.055</t>
+          <t>51568.4862798301</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>0.049</t>
+          <t>46146.3839761602</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>47050.1323470546</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>0.052</t>
+          <t>49082.6197287359</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>47197.3214147598</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>0.052</t>
+          <t>48773.947297842</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>0.054</t>
+          <t>50855.108779853</t>
         </is>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>0.057</t>
+          <t>54193.6142144632</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>0.059</t>
+          <t>55630.4955519315</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>0.062</t>
+          <t>58854.9216126456</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>0.072</t>
+          <t>68418.4769752945</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>0.075</t>
+          <t>70880.6860637712</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>0.081</t>
+          <t>76590.7226063639</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>0.083</t>
+          <t>78275.0183680865</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Indonésia</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3329,144 +3334,144 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>0.125</t>
+          <t>165890.380114723</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0.137</t>
+          <t>181566.639091862</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0.158</t>
+          <t>209923.175376243</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>225755.190750702</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0.196</t>
+          <t>260676.09661058</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.238</t>
+          <t>316344.332719934</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.257</t>
+          <t>341481.457521538</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.253</t>
+          <t>336420.234393454</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0.249</t>
+          <t>330774.073212742</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0.272</t>
+          <t>361352.565961257</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>0.317</t>
+          <t>421149.811703597</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>477662.524872948</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>557942.716026678</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>0.417</t>
+          <t>553910.147966076</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>0.451</t>
+          <t>598548.268723215</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>0.599</t>
+          <t>795567.444156713</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>0.637</t>
+          <t>845887.769296598</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>917077.057902683</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>0.669</t>
+          <t>888891.742074571</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>0.722</t>
+          <t>958877.703613374</t>
         </is>
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>0.911</t>
+          <t>1210312.89356889</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>0.975</t>
+          <t>1295405.20036971</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>1.094</t>
+          <t>1452887.6595706</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>1.048</t>
+          <t>1391925.11548332</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>1.125</t>
+          <t>1494082.63864455</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>1.278</t>
+          <t>1697719.11932195</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1859751.85008617</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Índia</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3476,144 +3481,144 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>70340.0321901061</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>0.069</t>
+          <t>81101.0468317506</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>0.071</t>
+          <t>83956.4083973361</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>39193.497651996</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>58564.8219745584</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>0.061</t>
+          <t>72501.046511623</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>0.061</t>
+          <t>71528.9169857739</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>0.069</t>
+          <t>81618.0113548565</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>0.076</t>
+          <t>89947.3004020606</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>0.074</t>
+          <t>87350.6694412581</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>0.079</t>
+          <t>93586.870812827</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>0.105</t>
+          <t>123821.007512098</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>0.107</t>
+          <t>126042.033508475</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>0.118</t>
+          <t>139837.352629988</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>165787.759881353</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>0.202</t>
+          <t>238310.467519986</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>0.212</t>
+          <t>250302.63880804</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>0.248</t>
+          <t>292687.494455779</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>0.218</t>
+          <t>257587.858408676</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>0.218</t>
+          <t>257646.142322582</t>
         </is>
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>0.253</t>
+          <t>298650.316321967</t>
         </is>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>0.281</t>
+          <t>332037.198144167</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>0.287</t>
+          <t>339245.512684939</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>0.284</t>
+          <t>335166.216594092</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>0.326</t>
+          <t>384732.880950686</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>0.345</t>
+          <t>408032.154760258</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>0.364</t>
+          <t>430059.685493065</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Irlanda</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3623,144 +3628,144 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>30766.9413116375</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>34391.0710239077</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>0.037</t>
+          <t>41014.8621737497</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>0.041</t>
+          <t>45414.6842436254</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>0.044</t>
+          <t>48958.2209374259</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>0.052</t>
+          <t>57494.291653001</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>0.058</t>
+          <t>64562.826266359</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>66445.4305023572</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>77508.7177038802</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>0.072</t>
+          <t>80213.8704604182</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>0.079</t>
+          <t>87871.2669886663</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>0.086</t>
+          <t>95331.1175449154</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>0.092</t>
+          <t>102645.076309862</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>0.092</t>
+          <t>101878.009337695</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>0.095</t>
+          <t>105170.009295505</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>89002.2347156742</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>0.084</t>
+          <t>93184.080264209</t>
         </is>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>88398.8396526396</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>0.083</t>
+          <t>92157.3318483547</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>0.087</t>
+          <t>96121.8311015263</t>
         </is>
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>0.113</t>
+          <t>123592.380540375</t>
         </is>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>0.113</t>
+          <t>123333.979391392</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>0.132</t>
+          <t>144746.728988985</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>154141.878912654</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>0.165</t>
+          <t>180420.917449309</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>0.173</t>
+          <t>188950.444074025</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>0.169</t>
+          <t>185097.649061733</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Itália</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3770,144 +3775,144 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>0.483</t>
+          <t>546801.43253196</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>0.559</t>
+          <t>632303.995894648</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>0.593</t>
+          <t>671341.131656272</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>0.564</t>
+          <t>637737.96833091</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>0.629</t>
+          <t>711245.695197224</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>0.667</t>
+          <t>754872.652042531</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>0.697</t>
+          <t>788619.080642554</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>813961.707932353</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>848816.529147626</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>0.774</t>
+          <t>875707.245197116</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>0.795</t>
+          <t>898937.325501687</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>0.824</t>
+          <t>931846.391821226</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>0.859</t>
+          <t>971156.693182024</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>0.858</t>
+          <t>970849.749523291</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>0.834</t>
+          <t>943160.820550274</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>984567.178093875</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>995500.457439242</t>
         </is>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>0.862</t>
+          <t>974756.007959492</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>0.852</t>
+          <t>964172.877176838</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>0.878</t>
+          <t>992940.655803307</t>
         </is>
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>0.893</t>
+          <t>1009962.02796404</t>
         </is>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>0.894</t>
+          <t>1011348.83164114</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>0.938</t>
+          <t>1060781.21360317</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>0.948</t>
+          <t>1071965.50865707</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>1097190.0803111</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>0.963</t>
+          <t>1089903.52770173</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>0.978</t>
+          <t>1105918.36035345</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Japão</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3917,144 +3922,144 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2.532</t>
+          <t>3523720.68318381</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2.241</t>
+          <t>3118644.02174256</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>3173563.45940162</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2.122</t>
+          <t>2953041.39262112</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2.516</t>
+          <t>3502634.12933994</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>3.33</t>
+          <t>4634459.05994517</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>2.938</t>
+          <t>4089911.79990845</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>2.518</t>
+          <t>3504823.46149419</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>2.232</t>
+          <t>3106099.1122097</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>2.159</t>
+          <t>3004763.76507818</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>3131770.2136553</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>2.103</t>
+          <t>2926998.17073158</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>1.798</t>
+          <t>2502813.24650446</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>1.971</t>
+          <t>2744133.51547049</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>2.206</t>
+          <t>3070384.62397411</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>2.462</t>
+          <t>3427392.75132963</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>2.566</t>
+          <t>3571465.85778109</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>2.733</t>
+          <t>3804567.49510953</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>2.122</t>
+          <t>2953492.03452023</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>2.102</t>
+          <t>2925109.44412302</t>
         </is>
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>2.256</t>
+          <t>3140143.54285605</t>
         </is>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>2.343</t>
+          <t>3261770.59038817</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2.188</t>
+          <t>3045441.90602695</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>2.215</t>
+          <t>3082581.39166052</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2.397</t>
+          <t>3336905.12422255</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>2.409</t>
+          <t>3353034.89964347</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>2.559</t>
+          <t>3562388.82133835</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Coreia do Sul</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -4064,144 +4069,144 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>0.222</t>
+          <t>292051.965163977</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>0.237</t>
+          <t>312299.96371662</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>0.241</t>
+          <t>317076.715106288</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>0.159</t>
+          <t>209449.457402412</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>0.217</t>
+          <t>286003.549313443</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>0.292</t>
+          <t>383999.307018593</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>0.285</t>
+          <t>375396.756504618</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>0.309</t>
+          <t>406742.343743314</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>0.306</t>
+          <t>403235.255563521</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>407677.791841395</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>0.366</t>
+          <t>481168.427849887</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>0.422</t>
+          <t>555414.988545693</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>0.417</t>
+          <t>547949.309759866</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>0.349</t>
+          <t>459541.141479631</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>0.327</t>
+          <t>430766.415009101</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>0.409</t>
+          <t>537665.613323611</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>0.416</t>
+          <t>546574.924738766</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>0.466</t>
+          <t>613056.423719062</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>0.503</t>
+          <t>662092.897772865</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>0.497</t>
+          <t>653548.332290575</t>
         </is>
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>0.618</t>
+          <t>813759.382840172</t>
         </is>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>0.629</t>
+          <t>827578.378985177</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>0.721</t>
+          <t>949151.561904739</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>0.636</t>
+          <t>836276.27258748</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>895043.435118942</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>0.695</t>
+          <t>915043.02714723</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>0.728</t>
+          <t>958738.095422895</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Lituânia</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -4211,144 +4216,144 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>2954.74495311511</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3648.25318937686</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>5047.57594504258</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>5716.07666096145</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>6325.07478764131</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>7028.56412974337</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>7255.89153829477</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>8866.7419676004</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>9306.45527524237</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>10495.8142679364</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>12453.4280823006</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>14733.6205942332</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>17800.423827152</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>19540.9257699191</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>16373.0091049903</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>15228.5294430017</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>17248.7459313975</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>18538.8847719732</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>18648.0767892857</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>19690.024808896</t>
         </is>
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>21211.4642830676</t>
         </is>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>22073.8981565666</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>24321.7572310901</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>27095.8085933414</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>27741.8218157938</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>28046.6596903281</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>29770.8904232942</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Luxemburgo</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -4358,144 +4363,144 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>10991.8880267262</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>10994.3597247422</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>11773.178741773</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>11604.8415952334</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>13340.289840451</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>14135.1146333711</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>15296.9224303501</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>14693.5065690068</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>16297.8804638985</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>16226.3499194262</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>18988.6148866997</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>18511.1841541741</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>20310.2125145467</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>23622.6469764836</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>23526.7958564103</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>23828.6817769018</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>24143.3292483383</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>26579.9591415886</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>25562.4367997852</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>29546.7659391252</t>
         </is>
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>28682.0466310782</t>
         </is>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>29908.7579034411</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>32493.3601488201</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>37404.1469818018</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>34971.3402419007</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>34334.1602428189</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>40656.9012552127</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Letônia</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -4505,144 +4510,144 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3436.50490543912</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3860.19581643201</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>4608.4914821859</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>4465.5646961974</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>4710.3768903168</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>5540.62405645469</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>5831.20702129323</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>6214.50500702787</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>6020.11786080372</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>5561.33396725271</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>7455.7965754</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>10977.9526284365</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>14348.3907668158</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>15637.0963318686</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>11587.4665744588</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>10500.4107620702</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>11006.8409300867</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>11924.8208974308</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>12785.9120942154</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>12424.9072756154</t>
         </is>
       </c>
       <c r="W33" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>13759.9585054562</t>
         </is>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>12719.1170600703</t>
         </is>
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>14130.2925712715</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>15666.7956884149</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>15722.3997659593</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>16337.72713499</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>16669.1956998692</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4652,144 +4657,144 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>0.103</t>
+          <t>136674.879606049</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>0.123</t>
+          <t>162749.130710149</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0.163</t>
+          <t>216716.55703049</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>0.184</t>
+          <t>244565.027743973</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>0.215</t>
+          <t>285317.483013017</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.268</t>
+          <t>355950.371655416</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.294</t>
+          <t>390274.806085421</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.287</t>
+          <t>381639.779334817</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>292795.66438923</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>278922.083194833</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>0.237</t>
+          <t>314956.675755881</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>0.256</t>
+          <t>340322.911289634</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>0.249</t>
+          <t>330244.222174807</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>0.244</t>
+          <t>323854.134752294</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>0.199</t>
+          <t>264927.958973443</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>0.236</t>
+          <t>313541.543055</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>0.255</t>
+          <t>338204.912887517</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>0.253</t>
+          <t>336222.341864539</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>0.256</t>
+          <t>340625.758600425</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>0.257</t>
+          <t>341690.447786755</t>
         </is>
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>0.316</t>
+          <t>419753.302984938</t>
         </is>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>0.241</t>
+          <t>319776.467172331</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>0.253</t>
+          <t>335822.196954274</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>0.246</t>
+          <t>326463.593522806</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>0.273</t>
+          <t>363323.446242933</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>0.276</t>
+          <t>366572.744464772</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>0.277</t>
+          <t>367580.02423635</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4799,144 +4804,144 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>1711.27844862229</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>1882.61005769901</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>2013.36224533431</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>2167.55291997709</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>2602.05430983992</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>2877.4606722632</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>2886.85500679897</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3140.00721140566</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3276.87771235376</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>2958.34657966116</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3272.14715280943</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3488.96289505426</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3507.72862861242</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3753.63369976609</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3878.10514381948</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3956.09182069376</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>4235.64650001662</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>4282.5930842336</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>4476.52973999133</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>4555.73094056974</t>
         </is>
       </c>
       <c r="W35" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>4459.13237187879</t>
         </is>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>5929.52744746062</t>
         </is>
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>5956.71451950168</t>
         </is>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>6664.22761873923</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>6306.08496710146</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>5634.29057278033</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>7864.81126723023</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Países Baixos</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4946,144 +4951,144 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>225947.494968802</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>0.184</t>
+          <t>230591.107212425</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>0.188</t>
+          <t>236457.007850728</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>0.219</t>
+          <t>275507.87110552</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>0.218</t>
+          <t>273844.70345569</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>301021.585879451</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>0.259</t>
+          <t>324632.342938535</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>0.272</t>
+          <t>341988.581821769</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>0.275</t>
+          <t>345305.139523169</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>0.285</t>
+          <t>358429.893708417</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>364616.027945753</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>0.305</t>
+          <t>383170.185214685</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>0.317</t>
+          <t>397938.210654842</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>0.337</t>
+          <t>422512.149110717</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>0.345</t>
+          <t>433377.139651349</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>0.341</t>
+          <t>428214.592352239</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>0.343</t>
+          <t>430731.3481027</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>0.345</t>
+          <t>432723.892331872</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>0.344</t>
+          <t>431812.486114059</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>0.367</t>
+          <t>460902.378360214</t>
         </is>
       </c>
       <c r="W36" t="inlineStr">
         <is>
-          <t>0.364</t>
+          <t>457647.760382438</t>
         </is>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>0.371</t>
+          <t>466393.783307416</t>
         </is>
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>0.394</t>
+          <t>494699.299941569</t>
         </is>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>0.406</t>
+          <t>509740.91255379</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>0.431</t>
+          <t>541695.706301758</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>0.443</t>
+          <t>556075.568997795</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>0.471</t>
+          <t>591082.97511917</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Polônia</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -5093,144 +5098,144 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>0.051</t>
+          <t>66034.3504430648</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>0.059</t>
+          <t>76052.7656096203</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>0.063</t>
+          <t>81223.4903431497</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>0.069</t>
+          <t>89144.0809847166</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>0.069</t>
+          <t>89150.8215310345</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>103918.465909051</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>0.094</t>
+          <t>122078.848503083</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>0.091</t>
+          <t>118695.566704202</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>0.078</t>
+          <t>101642.99845011</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>0.077</t>
+          <t>99665.7864001936</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>0.095</t>
+          <t>123095.499466174</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>0.106</t>
+          <t>137814.561683939</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>0.118</t>
+          <t>153542.650312249</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>0.153</t>
+          <t>198646.289751843</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>0.123</t>
+          <t>160125.444579735</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>0.144</t>
+          <t>186658.992726774</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>0.151</t>
+          <t>196234.850823623</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>0.153</t>
+          <t>198580.188645348</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>0.152</t>
+          <t>198472.662529531</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>0.161</t>
+          <t>209508.2648537</t>
         </is>
       </c>
       <c r="W37" t="inlineStr">
         <is>
-          <t>0.169</t>
+          <t>220612.43078019</t>
         </is>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>0.159</t>
+          <t>208022.534125541</t>
         </is>
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>0.185</t>
+          <t>241484.296828035</t>
         </is>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>0.188</t>
+          <t>245713.886855137</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>0.202</t>
+          <t>263847.346395346</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>0.212</t>
+          <t>276908.953705836</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>0.222</t>
+          <t>290581.706684615</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -5240,144 +5245,144 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>0.044</t>
+          <t>60739.8988316999</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>0.048</t>
+          <t>65610.0607341796</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>0.051</t>
+          <t>69924.9281291462</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>0.055</t>
+          <t>74933.5924317908</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>82393.393485504</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>0.069</t>
+          <t>94264.5643936264</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>0.072</t>
+          <t>98871.22254304</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>0.075</t>
+          <t>102819.244328746</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>0.078</t>
+          <t>106862.455430322</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>0.081</t>
+          <t>110380.752214314</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>0.085</t>
+          <t>116425.249695028</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>122740.844766693</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>0.095</t>
+          <t>129836.507611985</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>0.099</t>
+          <t>135026.726478246</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>0.096</t>
+          <t>131660.706972771</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>0.098</t>
+          <t>134167.244631477</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>0.097</t>
+          <t>132502.170145566</t>
         </is>
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>0.092</t>
+          <t>125834.439566683</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>0.093</t>
+          <t>128064.859646055</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>0.093</t>
+          <t>128101.108894688</t>
         </is>
       </c>
       <c r="W38" t="inlineStr">
         <is>
-          <t>0.097</t>
+          <t>133572.880416795</t>
         </is>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>0.101</t>
+          <t>138287.50877608</t>
         </is>
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>0.113</t>
+          <t>154680.154434521</t>
         </is>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>0.112</t>
+          <t>154142.396674406</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>0.116</t>
+          <t>159635.46937515</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>0.118</t>
+          <t>162093.740523391</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>0.121</t>
+          <t>165336.539831869</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Romênia</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -5387,144 +5392,144 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>16249.700326284</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>16529.846888785</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>18902.1053351338</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>23090.8321655679</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>21830.0218446614</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>27799.910999425</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>27587.3794478425</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>29742.2800634275</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>31364.6943887955</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>36498.2385472092</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>47017.7691076882</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>57423.3219926449</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>0.054</t>
+          <t>77731.7122107202</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>0.066</t>
+          <t>94693.9022288232</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>0.053</t>
+          <t>76711.6279323407</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>0.043</t>
+          <t>61933.0204006349</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>0.043</t>
+          <t>61722.0920368322</t>
         </is>
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>72039.6907232837</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>0.051</t>
+          <t>73639.3184069597</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>0.056</t>
+          <t>80496.4105629079</t>
         </is>
       </c>
       <c r="W39" t="inlineStr">
         <is>
-          <t>0.057</t>
+          <t>81919.8973525388</t>
         </is>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>0.055</t>
+          <t>79543.4385381852</t>
         </is>
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>0.074</t>
+          <t>106492.444114882</t>
         </is>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>0.083</t>
+          <t>120224.403629192</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>0.077</t>
+          <t>110735.193745144</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>0.086</t>
+          <t>124427.030587416</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>0.087</t>
+          <t>125497.724854007</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Rússia</t>
+          <t>43</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -5534,144 +5539,144 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>0.122</t>
+          <t>138224.983470056</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>137496.934365713</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>0.142</t>
+          <t>162004.477452287</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>0.098</t>
+          <t>111120.178401951</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>0.068</t>
+          <t>77514.4575075868</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>0.099</t>
+          <t>112700.889398815</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>0.133</t>
+          <t>151149.009950818</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>0.153</t>
+          <t>173786.239921343</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>0.155</t>
+          <t>175617.355441242</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>0.187</t>
+          <t>213988.258229026</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>306300.738239569</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>399507.213130329</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>0.428</t>
+          <t>484728.458440722</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>0.473</t>
+          <t>536314.628175413</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>0.384</t>
+          <t>437003.827754598</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>0.544</t>
+          <t>615277.487280096</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>0.694</t>
+          <t>786099.342887222</t>
         </is>
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>0.867</t>
+          <t>979521.940230206</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>0.901</t>
+          <t>1020568.32182278</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>0.796</t>
+          <t>897308.923035122</t>
         </is>
       </c>
       <c r="W40" t="inlineStr">
         <is>
-          <t>0.636</t>
+          <t>717140.805364426</t>
         </is>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>0.573</t>
+          <t>648536.955965353</t>
         </is>
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>0.726</t>
+          <t>818540.105204264</t>
         </is>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>0.682</t>
+          <t>771408.666763632</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>0.779</t>
+          <t>877862.585904995</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>0.792</t>
+          <t>893356.611552459</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>0.757</t>
+          <t>855034.2893792</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Eslováquia</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -5681,144 +5686,144 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>9375.05576285781</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>10611.2456508434</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>13239.6470547154</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>12567.5987021158</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>11538.1308570934</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>14088.7214315674</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>13682.874407064</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>15773.3391264996</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>18091.6239490678</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>19014.7298867996</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>23245.5081308663</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>25223.5471582575</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>33333.2824475445</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>34933.3272598544</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>35924.7986100508</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>40003.1817466212</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>41229.1909904213</t>
         </is>
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>43346.219257629</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>40866.9084923473</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>0.032</t>
+          <t>45220.6360521956</t>
         </is>
       </c>
       <c r="W41" t="inlineStr">
         <is>
-          <t>0.032</t>
+          <t>45241.9829005957</t>
         </is>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>41979.9500643039</t>
         </is>
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>0.035</t>
+          <t>49075.8540340394</t>
         </is>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>0.034</t>
+          <t>46784.0404246312</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>0.035</t>
+          <t>48590.5103729998</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>0.039</t>
+          <t>54398.1627670496</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>0.042</t>
+          <t>58325.2977733658</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Eslovênia</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -5828,144 +5833,144 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>13673.7089478468</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>13536.2340506829</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>14232.324083183</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>15419.524257846</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>16502.4574499901</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>16868.4449151554</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>19704.403059042</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>20021.8880271525</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>20704.8247292162</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>21946.7184291548</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>22838.6060144749</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>24318.8551194646</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>26879.6173211932</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>28938.3169381605</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>29225.1998416152</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>30373.7677583634</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>29829.91708192</t>
         </is>
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>29186.5285662523</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>30146.6510322244</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>30302.2136439727</t>
         </is>
       </c>
       <c r="W42" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>31656.5198095324</t>
         </is>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>32481.6865855105</t>
         </is>
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>34719.8665107995</t>
         </is>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>36783.499845472</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>37352.3669762304</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>41299.0840447624</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>42481.5512373978</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Suécia</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -5975,144 +5980,144 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>0.112</t>
+          <t>165107.567166635</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>0.133</t>
+          <t>195358.649371439</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>0.132</t>
+          <t>193638.076023315</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>0.135</t>
+          <t>198695.245091172</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>0.139</t>
+          <t>205151.217551965</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>0.163</t>
+          <t>239264.834649256</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>0.173</t>
+          <t>254868.811806479</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>0.181</t>
+          <t>266564.005415377</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>0.179</t>
+          <t>262831.819109374</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>0.177</t>
+          <t>259606.085282976</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>0.177</t>
+          <t>259963.607811728</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>0.188</t>
+          <t>276084.421367692</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>0.202</t>
+          <t>297523.501222171</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>293648.126715897</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>0.183</t>
+          <t>268907.982843353</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>0.204</t>
+          <t>300200.090575927</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>0.235</t>
+          <t>345977.434473723</t>
         </is>
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>0.243</t>
+          <t>356691.090741492</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>0.249</t>
+          <t>366070.753687939</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>0.241</t>
+          <t>354769.713455252</t>
         </is>
       </c>
       <c r="W43" t="inlineStr">
         <is>
-          <t>0.261</t>
+          <t>384188.584200031</t>
         </is>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>0.257</t>
+          <t>378677.624032812</t>
         </is>
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>0.267</t>
+          <t>392247.809770849</t>
         </is>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>0.285</t>
+          <t>418553.799968068</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>0.289</t>
+          <t>424784.019598538</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>0.275</t>
+          <t>404474.415715241</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>441509.956585209</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Turquia</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -6122,144 +6127,144 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>34792.3800870527</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>0.039</t>
+          <t>42860.7753386899</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>55134.1923077381</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>0.056</t>
+          <t>62520.4393987251</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>66714.7121048819</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>0.076</t>
+          <t>84515.2793093486</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>0.062</t>
+          <t>69224.4659629267</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>0.075</t>
+          <t>82979.8880707985</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>0.086</t>
+          <t>95424.7083036087</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>0.107</t>
+          <t>119090.144852509</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>0.139</t>
+          <t>154010.066580625</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>0.156</t>
+          <t>173496.119888216</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>0.182</t>
+          <t>201827.8134092</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>0.193</t>
+          <t>213782.414600877</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>0.171</t>
+          <t>189188.836016872</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>0.251</t>
+          <t>278511.825097177</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>0.243</t>
+          <t>268995.942474624</t>
         </is>
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>0.276</t>
+          <t>306564.602400625</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>0.297</t>
+          <t>329704.691368249</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>333115.00766892</t>
         </is>
       </c>
       <c r="W44" t="inlineStr">
         <is>
-          <t>0.333</t>
+          <t>368734.211039537</t>
         </is>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>0.339</t>
+          <t>375892.907827243</t>
         </is>
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>0.332</t>
+          <t>367822.966698373</t>
         </is>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>0.292</t>
+          <t>323647.51080707</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>0.307</t>
+          <t>340094.853939917</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>0.304</t>
+          <t>337056.712457589</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>0.356</t>
+          <t>394520.752459096</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>China: Taiwan</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -6269,144 +6274,144 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>0.121</t>
+          <t>136603.736699757</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>0.141</t>
+          <t>158791.542359171</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>0.154</t>
+          <t>174425.136865166</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>0.157</t>
+          <t>177440.342504896</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>0.155</t>
+          <t>174549.874891059</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>248111.774763851</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>0.192</t>
+          <t>216421.623780419</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>0.181</t>
+          <t>204302.333488545</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>0.165</t>
+          <t>186836.78812236</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>0.162</t>
+          <t>182824.514112269</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>0.159</t>
+          <t>179157.793449945</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>181078.259997336</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>0.132</t>
+          <t>148854.757844004</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>0.128</t>
+          <t>144583.193589917</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>0.117</t>
+          <t>132568.841012229</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>0.146</t>
+          <t>164617.235781039</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>0.184</t>
+          <t>208047.374256571</t>
         </is>
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>0.201</t>
+          <t>226697.224774669</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>0.175</t>
+          <t>197282.404688934</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>0.189</t>
+          <t>213157.950012757</t>
         </is>
       </c>
       <c r="W45" t="inlineStr">
         <is>
-          <t>0.183</t>
+          <t>206278.94565608</t>
         </is>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>0.206</t>
+          <t>233190.110439203</t>
         </is>
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>236818.20663597</t>
         </is>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>0.188</t>
+          <t>212214.424283913</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>0.226</t>
+          <t>255784.870041069</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>225842.970558483</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>0.216</t>
+          <t>244548.640377083</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -6416,144 +6421,144 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>3.369</t>
+          <t>4465648.69239676</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>3.656</t>
+          <t>4846117.38731125</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>4.268</t>
+          <t>5658374.79482557</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>4.743</t>
+          <t>6288010.57685808</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>5.322</t>
+          <t>7055059.18953065</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>6.372</t>
+          <t>8447583.75895968</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>7.113</t>
+          <t>9430150.62081893</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>6.828</t>
+          <t>9052202.33477991</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>5.658</t>
+          <t>7500636.80968186</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>5.69</t>
+          <t>7543276.9902051</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>5.763</t>
+          <t>7640546.67235728</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>6.343</t>
+          <t>8409240.62247193</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>6.126</t>
+          <t>8120824.93978851</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>5.754</t>
+          <t>7628174.46764566</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>6.076</t>
+          <t>8054379.89997374</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>6.27</t>
+          <t>8312252.244406</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>5.966</t>
+          <t>7909554.23395834</t>
         </is>
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>7.262</t>
+          <t>9627025.34132363</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>6.708</t>
+          <t>8893233.17400192</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>6.879</t>
+          <t>9119755.81637822</t>
         </is>
       </c>
       <c r="W46" t="inlineStr">
         <is>
-          <t>9.053</t>
+          <t>12001999.0255197</t>
         </is>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>9.344</t>
+          <t>12387261.9735592</t>
         </is>
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>9.729</t>
+          <t>12897962.247761</t>
         </is>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>9.904</t>
+          <t>13130097.1547974</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>10.506</t>
+          <t>13927356.6503548</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>10.695</t>
+          <t>14178177.1790775</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>11.255</t>
+          <t>14921136.6436109</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Resto do mundo</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -6565,7 +6570,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Mundo</t>
+          <t>46</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -6575,144 +6580,144 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>13.061</t>
+          <t>16402957.1369738</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>13.623</t>
+          <t>17071159.6397211</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>15.042</t>
+          <t>18893014.4522787</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>15.458</t>
+          <t>19468101.9274015</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>16.975</t>
+          <t>21398439.910887</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>20.15</t>
+          <t>25544137.5235769</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>20.793</t>
+          <t>26338545.9681022</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>20.319</t>
+          <t>25651516.5836977</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>18.742</t>
+          <t>23494153.6235755</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>18.866</t>
+          <t>23617253.4230231</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>20.117</t>
+          <t>25173611.5038354</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>21.722</t>
+          <t>27179641.7627194</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>22.117</t>
+          <t>27552940.6342802</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>22.528</t>
+          <t>28015829.5199088</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>23.107</t>
+          <t>28873203.4289683</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>25.969</t>
+          <t>32474939.5598421</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>27.335</t>
+          <t>34182684.025373</t>
         </is>
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>30.455</t>
+          <t>38174578.6055611</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>29.889</t>
+          <t>37393920.4434314</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>30.539</t>
+          <t>38229805.9432173</t>
         </is>
       </c>
       <c r="W48" t="inlineStr">
         <is>
-          <t>35.036</t>
+          <t>44145415.2624007</t>
         </is>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>35.58</t>
+          <t>44800424.9596128</t>
         </is>
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>37.279</t>
+          <t>46963148.1094301</t>
         </is>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>37.58</t>
+          <t>47375833.9038918</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>39.987</t>
+          <t>50445053.9151983</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>41.162</t>
+          <t>51943331.6246279</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>42.998</t>
+          <t>54302403.9183497</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Croácia</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -6722,144 +6727,144 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>8810.67401141436</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>9089.12465309813</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>10353.763058383</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>12455.5264042534</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>11944.3227066933</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>13234.3259587683</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>14663.727208711</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>14057.6991093612</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>14867.116319006</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>17066.0871160631</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>18625.6354199853</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>20365.3668044781</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>22875.3700304322</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>24628.0922674143</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>23976.9405893918</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>24645.984494581</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>22999.189922054</t>
         </is>
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>21917.7046384386</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>22432.6929545626</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>23396.5646471618</t>
         </is>
       </c>
       <c r="W49" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>23514.558127687</t>
         </is>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>24487.7718891614</t>
         </is>
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>25909.7981529896</t>
         </is>
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>26122.3238092254</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>27684.64605867</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>27218.5135733675</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>27371.3425298287</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Suíça</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -6869,144 +6874,144 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>0.135</t>
+          <t>148936.732161773</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>0.134</t>
+          <t>148511.01320058</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>0.144</t>
+          <t>159126.445473367</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>166030.112547981</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>0.147</t>
+          <t>162368.534724205</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>0.154</t>
+          <t>170695.004703828</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>0.168</t>
+          <t>186364.326669966</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>0.175</t>
+          <t>193570.735212041</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>0.177</t>
+          <t>196163.805797197</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>188511.547257937</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>0.176</t>
+          <t>194375.341431725</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>0.185</t>
+          <t>204760.701772362</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>210490.404530534</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>0.202</t>
+          <t>223620.603102401</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>0.222</t>
+          <t>246195.314933028</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>265650.350460009</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>0.258</t>
+          <t>285640.590203818</t>
         </is>
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>0.287</t>
+          <t>317476.324548933</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>0.289</t>
+          <t>319814.567204229</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
         <is>
-          <t>0.272</t>
+          <t>301196.272676591</t>
         </is>
       </c>
       <c r="W50" t="inlineStr">
         <is>
-          <t>0.315</t>
+          <t>349094.077875866</t>
         </is>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>0.325</t>
+          <t>359882.20203635</t>
         </is>
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>0.338</t>
+          <t>373707.431473059</t>
         </is>
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>321416.689848154</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>0.329</t>
+          <t>364151.621449716</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>0.311</t>
+          <t>343804.899921721</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>0.352</t>
+          <t>389631.942625551</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Noruega</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -7016,144 +7021,144 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>0.062</t>
+          <t>71911.9890032507</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>0.066</t>
+          <t>76487.7878507885</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>0.071</t>
+          <t>82583.8815209825</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>0.071</t>
+          <t>82423.9993062133</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>0.078</t>
+          <t>90319.7709603358</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>0.088</t>
+          <t>101898.911410159</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>0.092</t>
+          <t>106252.649843664</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>0.103</t>
+          <t>119017.573669313</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>0.101</t>
+          <t>117132.542306395</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>0.102</t>
+          <t>118098.667649002</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>0.112</t>
+          <t>129821.99274502</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>0.123</t>
+          <t>141962.294779231</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>0.139</t>
+          <t>161443.564713639</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>0.149</t>
+          <t>172122.265759009</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>0.139</t>
+          <t>161472.229757147</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>185060.277752672</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>0.172</t>
+          <t>199442.44419697</t>
         </is>
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>0.189</t>
+          <t>219308.917508473</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>0.208</t>
+          <t>241292.027846066</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>0.204</t>
+          <t>236399.329883004</t>
         </is>
       </c>
       <c r="W51" t="inlineStr">
         <is>
-          <t>0.177</t>
+          <t>205592.493537299</t>
         </is>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>208472.998907364</t>
         </is>
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>0.182</t>
+          <t>210531.206980142</t>
         </is>
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>0.182</t>
+          <t>210595.369272763</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>0.186</t>
+          <t>215400.061591489</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>0.197</t>
+          <t>228789.260466344</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>232689.712134981</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Africa do Sul</t>
+          <t>45</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -7163,144 +7168,144 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>0.067</t>
+          <t>75973.5802921815</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>0.066</t>
+          <t>74985.5158153862</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>0.073</t>
+          <t>82696.4908532834</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>0.065</t>
+          <t>74197.7074195594</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>0.069</t>
+          <t>78680.514121566</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>0.077</t>
+          <t>87935.3673307417</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>0.068</t>
+          <t>76720.1806726104</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>67583.6415879926</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>0.079</t>
+          <t>90023.7024499083</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>0.093</t>
+          <t>104921.645178953</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>0.101</t>
+          <t>114806.862372878</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>0.104</t>
+          <t>118093.469882367</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>0.101</t>
+          <t>114239.569961311</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>0.089</t>
+          <t>100351.57521963</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>0.093</t>
+          <t>105251.120070298</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>0.122</t>
+          <t>138089.638278901</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>0.123</t>
+          <t>139136.552258574</t>
         </is>
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>0.124</t>
+          <t>139606.380145267</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>0.107</t>
+          <t>121294.546635586</t>
         </is>
       </c>
       <c r="V52" t="inlineStr">
         <is>
-          <t>0.098</t>
+          <t>110598.201132129</t>
         </is>
       </c>
       <c r="W52" t="inlineStr">
         <is>
-          <t>0.102</t>
+          <t>115650.888230701</t>
         </is>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>0.085</t>
+          <t>95653.3980989815</t>
         </is>
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>0.106</t>
+          <t>119339.240032963</t>
         </is>
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>0.108</t>
+          <t>122175.340546304</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>123918.699781616</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>0.111</t>
+          <t>125717.674148669</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>0.112</t>
+          <t>126382.581345263</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Resto do mundo - Asia</t>
+          <t>47</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -7310,144 +7315,144 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>0.395</t>
+          <t>442009.052479734</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>0.449</t>
+          <t>503143.382555743</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>0.494</t>
+          <t>553286.688403256</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>0.461</t>
+          <t>516247.941200953</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>0.491</t>
+          <t>549294.425003481</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>0.593</t>
+          <t>663852.964919878</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>672145.301066017</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>0.621</t>
+          <t>695528.847895902</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>626508.443024929</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>0.558</t>
+          <t>624957.276273511</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>0.626</t>
+          <t>700882.747845045</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>0.721</t>
+          <t>807606.938475453</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>0.792</t>
+          <t>886389.451699192</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>0.824</t>
+          <t>922996.356290106</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>973836.14761402</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>1.057</t>
+          <t>1182858.71529125</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>1.158</t>
+          <t>1296772.23530917</t>
         </is>
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>1.359</t>
+          <t>1521857.07589896</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>1.399</t>
+          <t>1566720.78027757</t>
         </is>
       </c>
       <c r="V53" t="inlineStr">
         <is>
-          <t>1.478</t>
+          <t>1654305.87625806</t>
         </is>
       </c>
       <c r="W53" t="inlineStr">
         <is>
-          <t>1.621</t>
+          <t>1815093.566414</t>
         </is>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>1.802</t>
+          <t>2017183.60923772</t>
         </is>
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>1.872</t>
+          <t>2095502.26025806</t>
         </is>
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>1.785</t>
+          <t>1998738.28382713</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2.022</t>
+          <t>2263677.17848798</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>2.112</t>
+          <t>2364903.06367775</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>2.245</t>
+          <t>2513826.40436361</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Resto do mundo - America</t>
+          <t>50</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -7457,144 +7462,144 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>0.311</t>
+          <t>353936.583233514</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>0.333</t>
+          <t>378743.314827232</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>0.398</t>
+          <t>453047.944596949</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>0.434</t>
+          <t>494673.444672901</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>0.442</t>
+          <t>503833.623992683</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>0.524</t>
+          <t>596388.866629703</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>0.538</t>
+          <t>612242.588510416</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>0.398</t>
+          <t>452975.752793312</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>0.343</t>
+          <t>390713.551143525</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>0.363</t>
+          <t>413496.633661557</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>0.433</t>
+          <t>492488.844457846</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>0.494</t>
+          <t>561999.364340558</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>0.525</t>
+          <t>597073.873878336</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>0.584</t>
+          <t>664545.503666832</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>0.612</t>
+          <t>696482.235981962</t>
         </is>
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>0.741</t>
+          <t>842971.188999391</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>0.817</t>
+          <t>930047.963937269</t>
         </is>
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>0.979</t>
+          <t>1114771.12824581</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>0.999</t>
+          <t>1137853.97207971</t>
         </is>
       </c>
       <c r="V54" t="inlineStr">
         <is>
-          <t>0.992</t>
+          <t>1129958.77823642</t>
         </is>
       </c>
       <c r="W54" t="inlineStr">
         <is>
-          <t>1.191</t>
+          <t>1356187.79327453</t>
         </is>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>1.125</t>
+          <t>1280801.63162372</t>
         </is>
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>1.196</t>
+          <t>1361947.05194541</t>
         </is>
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>1.089</t>
+          <t>1239975.09060905</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>1.079</t>
+          <t>1228488.39546359</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>1.043</t>
+          <t>1187340.00050766</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>1.076</t>
+          <t>1224841.12521708</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Resto do mundo - Europa</t>
+          <t>48</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -7604,144 +7609,144 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>0.062</t>
+          <t>70287.8944766489</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>0.063</t>
+          <t>71609.2807042965</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>79724.0218405472</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>0.063</t>
+          <t>71943.224384307</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>0.055</t>
+          <t>62946.8565664394</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>0.056</t>
+          <t>63487.6882197162</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>0.073</t>
+          <t>83227.9982188595</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>0.077</t>
+          <t>88102.9116143009</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>0.074</t>
+          <t>84803.8375672419</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>0.081</t>
+          <t>92803.5356582779</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>0.096</t>
+          <t>109733.324824004</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>0.121</t>
+          <t>138134.491117405</t>
         </is>
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>0.149</t>
+          <t>169626.50620534</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>0.169</t>
+          <t>192463.340572459</t>
         </is>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>0.115</t>
+          <t>131071.078080303</t>
         </is>
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>0.147</t>
+          <t>167742.659362229</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>0.164</t>
+          <t>187350.095174757</t>
         </is>
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>0.181</t>
+          <t>206780.445067277</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>0.189</t>
+          <t>215851.985236815</t>
         </is>
       </c>
       <c r="V55" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>194069.11057918</t>
         </is>
       </c>
       <c r="W55" t="inlineStr">
         <is>
-          <t>0.155</t>
+          <t>176625.686810681</t>
         </is>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>0.157</t>
+          <t>179370.850172061</t>
         </is>
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>0.175</t>
+          <t>200244.904447387</t>
         </is>
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>0.168</t>
+          <t>191543.650779169</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>217250.6782322</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>0.198</t>
+          <t>226719.70804668</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>0.227</t>
+          <t>259284.948247947</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Resto do mundo - Africa</t>
+          <t>49</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -7751,144 +7756,144 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>0.127</t>
+          <t>148289.168540906</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>0.145</t>
+          <t>169173.888903768</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>186906.672310552</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>0.169</t>
+          <t>197965.330951391</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>210865.374224377</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>0.222</t>
+          <t>259341.629800707</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>0.236</t>
+          <t>275976.775921047</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>0.233</t>
+          <t>271632.173939403</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>0.235</t>
+          <t>275184.291514859</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>0.246</t>
+          <t>287516.585127763</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>0.292</t>
+          <t>341781.648538343</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>0.339</t>
+          <t>395814.157786551</t>
         </is>
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>0.358</t>
+          <t>418800.336055507</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>502585.431919273</t>
         </is>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>0.403</t>
+          <t>471613.240601077</t>
         </is>
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>0.456</t>
+          <t>533299.888110825</t>
         </is>
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>0.546</t>
+          <t>638159.314292381</t>
         </is>
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>678034.594325458</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>0.601</t>
+          <t>703814.164186615</t>
         </is>
       </c>
       <c r="V56" t="inlineStr">
         <is>
-          <t>0.667</t>
+          <t>780552.995271117</t>
         </is>
       </c>
       <c r="W56" t="inlineStr">
         <is>
-          <t>0.731</t>
+          <t>855942.12098033</t>
         </is>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>0.698</t>
+          <t>817562.766851334</t>
         </is>
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>0.685</t>
+          <t>801179.641228299</t>
         </is>
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>0.724</t>
+          <t>847244.97839317</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>0.787</t>
+          <t>921319.439302112</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>0.815</t>
+          <t>954032.554114371</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>994409.912392626</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Resto do mundo - Oriente Medio</t>
+          <t>51</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -7898,137 +7903,137 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>0.216</t>
+          <t>255245.846764154</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>0.246</t>
+          <t>291093.547545846</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>343314.231995681</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>0.298</t>
+          <t>352071.900588755</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>378859.228048395</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>0.409</t>
+          <t>484284.353972462</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>0.395</t>
+          <t>467214.040229358</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>0.435</t>
+          <t>514942.364266447</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>0.386</t>
+          <t>456175.70764792</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>0.398</t>
+          <t>471018.58243147</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>0.477</t>
+          <t>563827.04919024</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>0.548</t>
+          <t>647876.982359182</t>
         </is>
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>0.606</t>
+          <t>716401.12059125</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>0.687</t>
+          <t>812526.729264591</t>
         </is>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>816280.759611454</t>
         </is>
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>0.822</t>
+          <t>971632.687539123</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t>0.921</t>
+          <t>1089461.28811001</t>
         </is>
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>1.069</t>
+          <t>1264063.82549927</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>1230513.80275352</t>
         </is>
       </c>
       <c r="V57" t="inlineStr">
         <is>
-          <t>1.055</t>
+          <t>1247351.03652409</t>
         </is>
       </c>
       <c r="W57" t="inlineStr">
         <is>
-          <t>1.186</t>
+          <t>1403211.50811401</t>
         </is>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>1.203</t>
+          <t>1422490.4326512</t>
         </is>
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>1.221</t>
+          <t>1444117.81854248</t>
         </is>
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>1.256</t>
+          <t>1485963.01922653</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>1.434</t>
+          <t>1696328.73696081</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>1.476</t>
+          <t>1745315.19325189</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>1.517</t>
+          <t>1794215.18906869</t>
         </is>
       </c>
     </row>
@@ -8070,6 +8075,11 @@
           <t>compensation.empe.s.us</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8104,6 +8114,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>EXI382</t>
